--- a/website/examples/example_odk_svg.select.xlsx
+++ b/website/examples/example_odk_svg.select.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R0c11c506e02d4a6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rb79e6f24ea6a4512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Re4ae19b45ff143fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R8ec1f28dd2254dfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Ra3352a1b94694801"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Ra1930291bbda4e8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -304,7 +304,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='svg.select',input_svg_name='bodymap_black.svg',input_selection_mode='sequence',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='svg.select',input_svg_name='bodymap_black.svg',input_selection_mode='sequence',return_mode='flat')</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str"/>
       <x:c r="G2" s="4" t="str"/>
